--- a/docs/ap32_fiche_registre_gestion_stages.xlsx
+++ b/docs/ap32_fiche_registre_gestion_stages.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\sio2\SIO2-20252026\ap32-stages-apirest\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SIO2\TitouanGoinard\ap32-stages-apirest\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E8D243-4EC8-4455-8B7A-77A6EB2D6D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677BBDA4-98EC-4570-AA05-68616FBD6D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GestionStages_FicheRegistre" sheetId="1" r:id="rId1"/>
@@ -183,7 +183,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="77">
   <si>
     <t>N/A</t>
   </si>
@@ -272,131 +272,172 @@
     <t>Durée illimitée</t>
   </si>
   <si>
-    <t xml:space="preserve">Nom, prénom, adresse mail
+    <t>État civil, identité, données d'identification, images…</t>
+  </si>
+  <si>
+    <t>Durée de conservation</t>
+  </si>
+  <si>
+    <t>Catégories de données personnelles concernées</t>
+  </si>
+  <si>
+    <t>Sous-finalité 3</t>
+  </si>
+  <si>
+    <t>Sous-finalité 2</t>
+  </si>
+  <si>
+    <t>Rechercher des organisations et contacts pour accueillir en stage les étudiants actuels</t>
+  </si>
+  <si>
+    <t>Sous-finalité 1</t>
+  </si>
+  <si>
+    <t>Gestion des stages</t>
+  </si>
+  <si>
+    <t>Finalité principale</t>
+  </si>
+  <si>
+    <t>Finalité(s) du traitement effectué</t>
+  </si>
+  <si>
+    <t>Société du DPO (si celui-ci est externe)</t>
+  </si>
+  <si>
+    <t>claude.coignat@lycee-basch.fr</t>
+  </si>
+  <si>
+    <t>02 99 54 44 43</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Rennes</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>15 avenue Charles Tillon</t>
+  </si>
+  <si>
+    <t>Claude Coignat</t>
+  </si>
+  <si>
+    <t>Délégué à la protection des données</t>
+  </si>
+  <si>
+    <t>annie.baraban@lycee-basch.fr</t>
+  </si>
+  <si>
+    <t>Annie Baraban</t>
+  </si>
+  <si>
+    <t>Responsable du traitement</t>
+  </si>
+  <si>
+    <t>Adresse mél</t>
+  </si>
+  <si>
+    <t>Téléphone</t>
+  </si>
+  <si>
+    <t>Ville</t>
+  </si>
+  <si>
+    <t>Code Postal</t>
+  </si>
+  <si>
+    <t>Adresse</t>
+  </si>
+  <si>
+    <t>Nom</t>
+  </si>
+  <si>
+    <t>Acteurs</t>
+  </si>
+  <si>
+    <t>Mise à jour du traitement</t>
+  </si>
+  <si>
+    <t>Date de création du traitement</t>
+  </si>
+  <si>
+    <t>0352009u-dpo-0100</t>
+  </si>
+  <si>
+    <t>N° / RÉF</t>
+  </si>
+  <si>
+    <t>Nom du traitement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description  du traitement  </t>
+  </si>
+  <si>
+    <t>Consulter les guides et définitions sur le site de la CNIL</t>
+  </si>
+  <si>
+    <t>Fiche de registre du traitement Gestion des stages</t>
+  </si>
+  <si>
+    <t>Catégorie de personnes 2</t>
+  </si>
+  <si>
+    <t>Etudiants de la section</t>
+  </si>
+  <si>
+    <t>Salariés des organisations accueillant les stagiaires</t>
+  </si>
+  <si>
+    <t>Personnel enseignant de la section STS-SIO</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nom, prénom, adresse mail, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">adresse (étudiant), n° Tel (étudiant et salariés), date de naissance (étudiant), fonction (salariés) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF004A99"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
-  </si>
-  <si>
-    <t>État civil, identité, données d'identification, images…</t>
-  </si>
-  <si>
-    <t>Durée de conservation</t>
-  </si>
-  <si>
-    <t>Catégories de données personnelles concernées</t>
-  </si>
-  <si>
-    <t>Sous-finalité 3</t>
-  </si>
-  <si>
-    <t>Sous-finalité 2</t>
-  </si>
-  <si>
-    <t>Rechercher des organisations et contacts pour accueillir en stage les étudiants actuels</t>
-  </si>
-  <si>
-    <t>Sous-finalité 1</t>
-  </si>
-  <si>
-    <t>Gestion des stages</t>
-  </si>
-  <si>
-    <t>Finalité principale</t>
-  </si>
-  <si>
-    <t>Finalité(s) du traitement effectué</t>
-  </si>
-  <si>
-    <t>Société du DPO (si celui-ci est externe)</t>
-  </si>
-  <si>
-    <t>claude.coignat@lycee-basch.fr</t>
-  </si>
-  <si>
-    <t>02 99 54 44 43</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>Rennes</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>15 avenue Charles Tillon</t>
-  </si>
-  <si>
-    <t>Claude Coignat</t>
-  </si>
-  <si>
-    <t>Délégué à la protection des données</t>
-  </si>
-  <si>
-    <t>annie.baraban@lycee-basch.fr</t>
-  </si>
-  <si>
-    <t>Annie Baraban</t>
-  </si>
-  <si>
-    <t>Responsable du traitement</t>
-  </si>
-  <si>
-    <t>Adresse mél</t>
-  </si>
-  <si>
-    <t>Téléphone</t>
-  </si>
-  <si>
-    <t>Ville</t>
-  </si>
-  <si>
-    <t>Code Postal</t>
-  </si>
-  <si>
-    <t>Adresse</t>
-  </si>
-  <si>
-    <t>Nom</t>
-  </si>
-  <si>
-    <t>Acteurs</t>
-  </si>
-  <si>
-    <t>Mise à jour du traitement</t>
-  </si>
-  <si>
-    <t>Date de création du traitement</t>
-  </si>
-  <si>
-    <t>0352009u-dpo-0100</t>
-  </si>
-  <si>
-    <t>N° / RÉF</t>
-  </si>
-  <si>
-    <t>Nom du traitement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description  du traitement  </t>
-  </si>
-  <si>
-    <t>Consulter les guides et définitions sur le site de la CNIL</t>
-  </si>
-  <si>
-    <t>Fiche de registre du traitement Gestion des stages</t>
-  </si>
-  <si>
-    <t>Catégorie de personnes 2</t>
-  </si>
-  <si>
-    <t>Etudiants de la section</t>
-  </si>
-  <si>
-    <t>Salariés des organisations accueillant les stagiaires</t>
-  </si>
-  <si>
-    <t>Personnel enseignant de la section STS-SIO</t>
+    </r>
+  </si>
+  <si>
+    <t>Salariés de l'entreprise accueillante</t>
+  </si>
+  <si>
+    <t>Création d'un utilisatur spécifique pour la consultation de la base de données</t>
+  </si>
+  <si>
+    <t>Historique des connexions</t>
+  </si>
+  <si>
+    <t>Création des logs de suivie de connection (nom utilisateur, mail, date, heures, minutes)</t>
+  </si>
+  <si>
+    <t>Répertorier les missions effectuées pendant le stage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non présent dans notre cas
+</t>
   </si>
 </sst>
 </file>
@@ -406,7 +447,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#&quot; &quot;##&quot; &quot;##&quot; &quot;##&quot; &quot;#0"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -491,6 +532,19 @@
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Georgia"/>
       <family val="1"/>
     </font>
@@ -707,7 +761,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -839,6 +893,35 @@
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -854,44 +937,25 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1208,26 +1272,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1001"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.08984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="66.81640625" customWidth="1"/>
-    <col min="2" max="2" width="23.453125" customWidth="1"/>
-    <col min="3" max="3" width="31.36328125" customWidth="1"/>
-    <col min="4" max="4" width="20.08984375" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" customWidth="1"/>
-    <col min="6" max="7" width="19.6328125" customWidth="1"/>
-    <col min="8" max="8" width="23.54296875" customWidth="1"/>
-    <col min="9" max="9" width="12.6328125" customWidth="1"/>
-    <col min="10" max="10" width="46.90625" customWidth="1"/>
-    <col min="11" max="11" width="11.08984375" customWidth="1"/>
-    <col min="12" max="26" width="8.81640625" customWidth="1"/>
-    <col min="27" max="1024" width="14.90625" customWidth="1"/>
-    <col min="1025" max="1025" width="11.08984375" customWidth="1"/>
+    <col min="1" max="1" width="66.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" customWidth="1"/>
+    <col min="3" max="3" width="31.42578125" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="7" width="19.5703125" customWidth="1"/>
+    <col min="8" max="8" width="23.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" customWidth="1"/>
+    <col min="10" max="10" width="46.85546875" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="26" width="8.85546875" customWidth="1"/>
+    <col min="27" max="1024" width="14.85546875" customWidth="1"/>
+    <col min="1025" max="1025" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="33.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
@@ -1241,7 +1305,7 @@
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -1260,15 +1324,15 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+    <row r="2" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="60"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
       <c r="I2" s="1"/>
       <c r="J2" s="33" t="str">
         <f>HYPERLINK("https://www.cnil.fr/fr/definition/traitement-de-donnees-caractere-personnel","► Traitement de données à caractère personnel")</f>
@@ -1291,9 +1355,9 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
@@ -1324,19 +1388,19 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
+        <v>62</v>
+      </c>
+      <c r="B4" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
       <c r="I4" s="1"/>
       <c r="J4" s="33" t="str">
         <f>HYPERLINK("https://www.cnil.fr/fr/definition/donnee-personnelle","► Données personnelles")</f>
@@ -1359,19 +1423,19 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
+      <c r="B5" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
       <c r="I5" s="1"/>
       <c r="J5" s="33" t="str">
         <f>HYPERLINK("https://www.cnil.fr/fr/definition/responsable-de-traitement","► Responsable de traitement")</f>
@@ -1394,19 +1458,19 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="48">
+        <v>59</v>
+      </c>
+      <c r="B6" s="61">
         <v>43246</v>
       </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
       <c r="I6" s="1"/>
       <c r="J6" s="33" t="str">
         <f>HYPERLINK("https://www.cnil.fr/fr/definition/donnee-sensible","► Données sensibles")</f>
@@ -1429,17 +1493,19 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
+        <v>58</v>
+      </c>
+      <c r="B7" s="66">
+        <v>45995</v>
+      </c>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
       <c r="I7" s="1"/>
       <c r="J7" s="33" t="str">
         <f>HYPERLINK("https://www.cnil.fr/fr/definition/finalite-dun-traitement","► Finalité du traitement")</f>
@@ -1462,7 +1528,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1493,30 +1559,30 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F9" s="39" t="s">
         <v>4</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="33" t="str">
@@ -1540,30 +1606,30 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H10" s="38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="33" t="str">
@@ -1587,30 +1653,30 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F11" s="36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="33" t="str">
@@ -1634,9 +1700,9 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="31" t="s">
         <v>0</v>
@@ -1666,7 +1732,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19"/>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -1694,9 +1760,9 @@
       <c r="Y13" s="26"/>
       <c r="Z13" s="26"/>
     </row>
-    <row r="14" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="24"/>
@@ -1724,19 +1790,19 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
+      <c r="B15" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="63"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1756,19 +1822,19 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
+      <c r="B16" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="64"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="64"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1788,17 +1854,19 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
+        <v>33</v>
+      </c>
+      <c r="B17" s="71" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1818,17 +1886,17 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
+        <v>32</v>
+      </c>
+      <c r="B18" s="65"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="65"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1848,7 +1916,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="22"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1876,21 +1944,21 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="54" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="54"/>
       <c r="D20" s="54"/>
-      <c r="E20" s="59" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="59"/>
+      <c r="E20" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
       <c r="I20" s="21"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1910,21 +1978,21 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:26" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="46" t="s">
+      <c r="B21" s="58" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
       <c r="I21" s="21"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1944,16 +2012,18 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:26" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="52"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="52"/>
+      <c r="B22" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
       <c r="H22" s="12"/>
       <c r="I22" s="20"/>
       <c r="J22" s="1"/>
@@ -1974,17 +2044,19 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:26" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
+      <c r="B23" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -2004,7 +2076,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -2032,7 +2104,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>25</v>
       </c>
@@ -2066,21 +2138,21 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="60" t="s">
+      <c r="B26" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="61" t="s">
-        <v>68</v>
-      </c>
-      <c r="F26" s="61"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -2100,21 +2172,21 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" s="60" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="61" t="s">
-        <v>69</v>
-      </c>
-      <c r="F27" s="61"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="61"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -2134,7 +2206,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2162,21 +2234,21 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="62" t="s">
+      <c r="B29" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="59" t="s">
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="F29" s="59"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="59"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -2196,21 +2268,21 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B30" s="60" t="s">
+      <c r="B30" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="60"/>
-      <c r="D30" s="60"/>
-      <c r="E30" s="63" t="s">
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="F30" s="63"/>
-      <c r="G30" s="63"/>
-      <c r="H30" s="63"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -2230,21 +2302,21 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="60" t="s">
+      <c r="B31" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="63" t="s">
-        <v>70</v>
-      </c>
-      <c r="F31" s="63"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -2264,17 +2336,21 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="64"/>
-      <c r="F32" s="64"/>
-      <c r="G32" s="64"/>
-      <c r="H32" s="64"/>
+      <c r="B32" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="70" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -2294,7 +2370,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16"/>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -2322,7 +2398,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>14</v>
       </c>
@@ -2356,21 +2432,21 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="53" t="s">
+      <c r="B35" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="53"/>
-      <c r="D35" s="53"/>
-      <c r="E35" s="67" t="s">
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="F35" s="67"/>
-      <c r="G35" s="67"/>
-      <c r="H35" s="67"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="49"/>
+      <c r="H35" s="49"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -2390,17 +2466,21 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="64"/>
-      <c r="G36" s="64"/>
-      <c r="H36" s="64"/>
+      <c r="B36" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="70" t="s">
+        <v>72</v>
+      </c>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -2420,17 +2500,21 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B37" s="53"/>
-      <c r="C37" s="53"/>
-      <c r="D37" s="53"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="50"/>
+      <c r="B37" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="47"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -2450,7 +2534,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
       <c r="B38" s="9"/>
       <c r="C38" s="8"/>
@@ -2478,7 +2562,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>6</v>
       </c>
@@ -2488,15 +2572,15 @@
       <c r="C39" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D39" s="65" t="s">
+      <c r="D39" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="E39" s="65"/>
-      <c r="F39" s="66" t="s">
+      <c r="E39" s="45"/>
+      <c r="F39" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="G39" s="66"/>
-      <c r="H39" s="66"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="46"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -2516,7 +2600,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>1</v>
       </c>
@@ -2524,11 +2608,11 @@
         <v>0</v>
       </c>
       <c r="C40" s="2"/>
-      <c r="D40" s="53"/>
-      <c r="E40" s="53"/>
-      <c r="F40" s="53"/>
-      <c r="G40" s="53"/>
-      <c r="H40" s="53"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="47"/>
+      <c r="G40" s="47"/>
+      <c r="H40" s="47"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -2548,969 +2632,996 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="42" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="44" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="45" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="46" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="47" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="48" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="41" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:H30"/>
     <mergeCell ref="D39:E39"/>
     <mergeCell ref="F39:H39"/>
     <mergeCell ref="D40:E40"/>
@@ -3527,33 +3638,6 @@
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="E31:H31"/>
     <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:H20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
